--- a/output/pdf_financials_xlsx/CTA.xlsx
+++ b/output/pdf_financials_xlsx/CTA.xlsx
@@ -1169,13 +1169,13 @@
         <v>0.032612</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.045001</v>
+        <v>-0.035343</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.039534</v>
+        <v>-0.04081</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.000751</v>
+        <v>-0.002027</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1359,13 +1359,13 @@
         <v>-0.004829</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0.000209</v>
@@ -1497,13 +1497,13 @@
         <v>-0.004829</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0.000209</v>
@@ -1897,13 +1897,13 @@
         <v>-87.1023744023931</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-931.8906605922551</v>
+        <v>-731.8906605922551</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>98.41182913472069</v>
+        <v>101.5881708652793</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>54.06767458603312</v>
+        <v>145.9323254139669</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>0</v>
@@ -1947,10 +1947,10 @@
         <v>-21.0221583736015</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>177.3598233995585</v>
+        <v>-177.3598233995585</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.131988431716968</v>
+        <v>-1.131988431716968</v>
       </c>
       <c r="L32" s="1" t="inlineStr">
         <is>
@@ -5044,10 +5044,10 @@
         <v>-0.004829</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.001389</v>
+        <v>-0.001389</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>0.000209</v>
@@ -21125,13 +21125,13 @@
         <v>-0.004829</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="O179" s="5" t="n">
-        <v>0.001389</v>
+        <v>-0.001389</v>
       </c>
       <c r="P179" s="5" t="n">
-        <v>0.000209</v>
+        <v>-0.000209</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -40200,10 +40200,10 @@
         </is>
       </c>
       <c r="N418" s="5" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="O418" s="5" t="n">
-        <v>0.000638</v>
+        <v>-0.000638</v>
       </c>
       <c r="P418" t="inlineStr">
         <is>
@@ -40516,10 +40516,10 @@
         <v>-0.004829</v>
       </c>
       <c r="N422" s="5" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="O422" s="5" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="P422" t="inlineStr">
         <is>
@@ -42093,10 +42093,10 @@
         <v>-0.004829</v>
       </c>
       <c r="M442" s="5" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="N442" s="5" t="n">
-        <v>0.040172</v>
+        <v>-0.040172</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CTA.xlsx
+++ b/output/pdf_financials_xlsx/CTA.xlsx
@@ -854,10 +854,10 @@
         <v>0.000638</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.000674</v>
       </c>
     </row>
     <row r="11">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.000659</v>
+        <v>0.000209</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.000799</v>
+        <v>0.000125</v>
       </c>
     </row>
     <row r="12">
@@ -2011,10 +2011,10 @@
         <v>0.000459</v>
       </c>
       <c r="M34" s="3" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>1.3e-05</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2103,10 +2103,10 @@
         <v>0.000459</v>
       </c>
       <c r="M36" s="3" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>1.3e-05</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2655,10 +2655,10 @@
         <v>7.8e-05</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000714</v>
+        <v>0.000696</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.000801</v>
+        <v>0.000788</v>
       </c>
     </row>
     <row r="49">
@@ -6185,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-7.2e-05</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -6231,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-7.2e-05</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24396,7 +24396,11 @@
           <t>Lease payment 10</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -27175,7 +27179,11 @@
           <t>Lease payment 11</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -35039,7 +35047,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -35355,7 +35363,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTA.xlsx
+++ b/output/pdf_financials_xlsx/CTA.xlsx
@@ -1747,16 +1747,16 @@
         <v>0.005727</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.008075000000000001</v>
+        <v>0.000232</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.01321</v>
+        <v>7.3e-05</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.001792</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.000554</v>
+        <v>6e-06</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -1793,16 +1793,16 @@
         <v>0.00155</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.015684</v>
+        <v>-0.023527</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.024231</v>
+        <v>-0.037368</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.003037</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.040726</v>
+        <v>0.040178</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>0.001389</v>
@@ -1843,16 +1843,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-54.98913119697077</v>
+        <v>-82.48720286094944</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-105.4851769622568</v>
+        <v>-162.6746767663576</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-13.4083885209713</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>72.25918631677933</v>
+        <v>71.28688277354908</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -5081,16 +5081,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.000232</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>7.3e-05</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -23292,7 +23292,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -24564,7 +24568,11 @@
           <t>Depreciation of right-of-use assets 6</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -41259,7 +41267,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -42456,7 +42468,11 @@
           <t>Depreciation of right-of-use assets 6</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CTA.xlsx
+++ b/output/pdf_financials_xlsx/CTA.xlsx
@@ -1154,19 +1154,19 @@
         <v>0.010952</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.005168</v>
+        <v>0.000691</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.037715</v>
+        <v>-0.007091</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.019111</v>
+        <v>-0.001005</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.014261</v>
+        <v>-0.000471</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.032612</v>
+        <v>0.000579</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0.035343</v>
@@ -1341,13 +1341,13 @@
         <v>-0.031832</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.013705</v>
+        <v>-0.006164</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.036577</v>
+        <v>-0.0321</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.003172</v>
+        <v>-0.033796</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.023288</v>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.007541</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.004477</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1882,19 +1882,19 @@
         <v>228.7385129490393</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-16.45388264510172</v>
+        <v>-2.200006367601643</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-92.24203291999902</v>
+        <v>-17.34292073275124</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-457.5293272683745</v>
+        <v>-24.06033038065597</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-60.02357001557305</v>
+        <v>-1.982406666947262</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-87.1023744023931</v>
+        <v>-1.546433054672685</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-731.8906605922551</v>
@@ -5523,34 +5523,34 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.000266</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>-0.001815</v>
+        <v>-0.001468</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.000255</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000643</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.000407</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.000189</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.000138</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.000205</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-4.5e-05</v>
       </c>
     </row>
     <row r="122">
@@ -20681,7 +20681,11 @@
           <t>Purchase of Common Shares 9</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -22271,7 +22275,11 @@
           <t>Purchase of Common Shares</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -22733,7 +22741,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -23450,7 +23462,11 @@
           <t>Accretion 15</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -25368,7 +25384,11 @@
           <t>Accretion 16</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -25595,7 +25615,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -26478,7 +26502,11 @@
           <t>Deferred income tax expense (recovery) 18</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -27586,7 +27614,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -28759,7 +28791,11 @@
           <t>Accretion 17</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -31319,7 +31355,11 @@
           <t>Deferred income tax expense (recovery) 19</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -32366,7 +32406,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E321" s="5" t="n">
         <v>0.137</v>
       </c>
@@ -32605,7 +32649,11 @@
           <t>Deferred income tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -33828,7 +33876,11 @@
           <t>Deferred income tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E339" s="5" t="n">
         <v>-0.613</v>
       </c>
@@ -44198,7 +44250,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -49792,7 +49848,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -49869,7 +49929,11 @@
           <t>Net loss from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -51698,7 +51762,11 @@
           <t>Net loss from discontinued operations 5a</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -55728,7 +55796,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E613" s="5" t="n">
         <v>0.613</v>
       </c>
